--- a/feat/passage-template2/ig/all-profiles.xlsx
+++ b/feat/passage-template2/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:35:10+00:00</t>
+    <t>2026-06-29T09:35:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
@@ -120,7 +120,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Patient</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Patient|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
